--- a/HWs/LIG_DATA.xlsx
+++ b/HWs/LIG_DATA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MSE\5820x\HWs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CB9E917-82DB-4A28-A839-4D2831425087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B20A1F-E36E-45C5-B5FB-0F4E2BE836CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="270" yWindow="375" windowWidth="20220" windowHeight="10545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,13 +27,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t>Power</t>
-  </si>
-  <si>
     <t>DPI</t>
-  </si>
-  <si>
-    <t>Defocus</t>
   </si>
   <si>
     <t>Sheet Conductance (1/ohm)</t>
@@ -46,6 +40,12 @@
   </si>
   <si>
     <t>Resistance (ohm)</t>
+  </si>
+  <si>
+    <t>Power (W)</t>
+  </si>
+  <si>
+    <t>Defocus (inch)</t>
   </si>
 </sst>
 </file>
@@ -380,25 +380,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
         <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">

--- a/HWs/LIG_DATA.xlsx
+++ b/HWs/LIG_DATA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MSE\5820x\HWs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B20A1F-E36E-45C5-B5FB-0F4E2BE836CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855BAB6D-741B-44CF-8155-B4C9AAD108DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="270" yWindow="375" windowWidth="20220" windowHeight="10545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>DPI</t>
   </si>
@@ -37,9 +37,6 @@
   </si>
   <si>
     <t>Speed (cm/s)</t>
-  </si>
-  <si>
-    <t>Resistance (ohm)</t>
   </si>
   <si>
     <t>Power (W)</t>
@@ -370,17 +367,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C580A198-721D-4C58-9C52-EC29E3E48762}">
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="11.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
         <v>3</v>
@@ -389,19 +387,16 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>58</v>
       </c>
@@ -415,18 +410,14 @@
         <v>-0.1</v>
       </c>
       <c r="E2">
-        <v>1.7</v>
+        <v>7.1757</v>
       </c>
       <c r="F2">
-        <f>E2*4.221</f>
-        <v>7.1757</v>
-      </c>
-      <c r="G2">
-        <f>1/F2</f>
+        <f>1/E2</f>
         <v>0.13935922627757572</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>60</v>
       </c>
@@ -439,19 +430,15 @@
       <c r="D3" s="1">
         <v>0.2</v>
       </c>
-      <c r="E3" s="1">
-        <v>1.7</v>
+      <c r="E3">
+        <v>7.1757</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F66" si="0">E3*4.221</f>
-        <v>7.1757</v>
-      </c>
-      <c r="G3">
-        <f t="shared" ref="G3:G66" si="1">1/F3</f>
+        <f t="shared" ref="F3:F66" si="0">1/E3</f>
         <v>0.13935922627757572</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>50</v>
       </c>
@@ -464,19 +451,15 @@
       <c r="D4" s="1">
         <v>-0.1</v>
       </c>
-      <c r="E4" s="1">
-        <v>2.1</v>
+      <c r="E4">
+        <v>8.8641000000000005</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>8.8641000000000005</v>
-      </c>
-      <c r="G4">
-        <f t="shared" si="1"/>
         <v>0.11281461174851366</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>56</v>
       </c>
@@ -490,18 +473,14 @@
         <v>-0.1</v>
       </c>
       <c r="E5">
-        <v>2.6</v>
+        <v>10.974600000000001</v>
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
-        <v>10.974600000000001</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="1"/>
         <v>9.1119494104568724E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>55</v>
       </c>
@@ -515,18 +494,14 @@
         <v>-0.2</v>
       </c>
       <c r="E6">
-        <v>2.7</v>
+        <v>11.396700000000001</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>11.396700000000001</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="1"/>
         <v>8.7744698026621729E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>54</v>
       </c>
@@ -540,18 +515,14 @@
         <v>0.3</v>
       </c>
       <c r="E7">
-        <v>2.8</v>
+        <v>11.8188</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>11.8188</v>
-      </c>
-      <c r="G7">
-        <f t="shared" si="1"/>
         <v>8.4610958811385251E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>53</v>
       </c>
@@ -565,18 +536,14 @@
         <v>-0.2</v>
       </c>
       <c r="E8">
-        <v>3.1</v>
+        <v>13.085100000000001</v>
       </c>
       <c r="F8">
         <f t="shared" si="0"/>
-        <v>13.085100000000001</v>
-      </c>
-      <c r="G8">
-        <f t="shared" si="1"/>
         <v>7.6422801507057644E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>70</v>
       </c>
@@ -590,18 +557,14 @@
         <v>-0.2</v>
       </c>
       <c r="E9">
-        <v>3.1</v>
+        <v>13.085100000000001</v>
       </c>
       <c r="F9">
         <f t="shared" si="0"/>
-        <v>13.085100000000001</v>
-      </c>
-      <c r="G9">
-        <f t="shared" si="1"/>
         <v>7.6422801507057644E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>61</v>
       </c>
@@ -614,19 +577,15 @@
       <c r="D10" s="1">
         <v>0.3</v>
       </c>
-      <c r="E10" s="1">
-        <v>3.2</v>
+      <c r="E10">
+        <v>13.507200000000001</v>
       </c>
       <c r="F10">
         <f t="shared" si="0"/>
-        <v>13.507200000000001</v>
-      </c>
-      <c r="G10">
-        <f t="shared" si="1"/>
         <v>7.4034588959962094E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>51</v>
       </c>
@@ -639,19 +598,15 @@
       <c r="D11" s="1">
         <v>0.2</v>
       </c>
-      <c r="E11" s="1">
-        <v>3.3</v>
+      <c r="E11">
+        <v>13.9293</v>
       </c>
       <c r="F11">
         <f t="shared" si="0"/>
-        <v>13.9293</v>
-      </c>
-      <c r="G11">
-        <f t="shared" si="1"/>
         <v>7.1791116567235969E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>36</v>
       </c>
@@ -665,18 +620,14 @@
         <v>0.3</v>
       </c>
       <c r="E12">
-        <v>3.3</v>
+        <v>13.9293</v>
       </c>
       <c r="F12">
         <f t="shared" si="0"/>
-        <v>13.9293</v>
-      </c>
-      <c r="G12">
-        <f t="shared" si="1"/>
         <v>7.1791116567235969E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>41</v>
       </c>
@@ -689,19 +640,15 @@
       <c r="D13" s="1">
         <v>-0.2</v>
       </c>
-      <c r="E13" s="1">
-        <v>3.3</v>
+      <c r="E13">
+        <v>13.9293</v>
       </c>
       <c r="F13">
         <f t="shared" si="0"/>
-        <v>13.9293</v>
-      </c>
-      <c r="G13">
-        <f t="shared" si="1"/>
         <v>7.1791116567235969E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>48</v>
       </c>
@@ -715,18 +662,14 @@
         <v>-0.1</v>
       </c>
       <c r="E14">
-        <v>3.4</v>
+        <v>14.3514</v>
       </c>
       <c r="F14">
         <f t="shared" si="0"/>
-        <v>14.3514</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="1"/>
         <v>6.9679613138787858E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>47</v>
       </c>
@@ -740,18 +683,14 @@
         <v>0.2</v>
       </c>
       <c r="E15">
-        <v>3.5</v>
+        <v>14.7735</v>
       </c>
       <c r="F15">
         <f t="shared" si="0"/>
-        <v>14.7735</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="1"/>
         <v>6.7688767049108201E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>39</v>
       </c>
@@ -765,18 +704,14 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>3.5</v>
+        <v>14.7735</v>
       </c>
       <c r="F16">
         <f t="shared" si="0"/>
-        <v>14.7735</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="1"/>
         <v>6.7688767049108201E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>53</v>
       </c>
@@ -790,18 +725,14 @@
         <v>-0.2</v>
       </c>
       <c r="E17">
-        <v>3.6</v>
+        <v>15.195600000000001</v>
       </c>
       <c r="F17">
         <f t="shared" si="0"/>
-        <v>15.195600000000001</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="1"/>
         <v>6.58085235199663E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>56</v>
       </c>
@@ -814,19 +745,15 @@
       <c r="D18" s="1">
         <v>0</v>
       </c>
-      <c r="E18" s="1">
-        <v>3.7</v>
+      <c r="E18">
+        <v>15.617700000000001</v>
       </c>
       <c r="F18">
         <f t="shared" si="0"/>
-        <v>15.617700000000001</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="1"/>
         <v>6.402991477618343E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>50</v>
       </c>
@@ -840,18 +767,14 @@
         <v>-0.1</v>
       </c>
       <c r="E19">
-        <v>3.7</v>
+        <v>15.617700000000001</v>
       </c>
       <c r="F19">
         <f t="shared" si="0"/>
-        <v>15.617700000000001</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="1"/>
         <v>6.402991477618343E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>69</v>
       </c>
@@ -865,18 +788,14 @@
         <v>0.3</v>
       </c>
       <c r="E20">
-        <v>3.7</v>
+        <v>15.617700000000001</v>
       </c>
       <c r="F20">
         <f t="shared" si="0"/>
-        <v>15.617700000000001</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="1"/>
         <v>6.402991477618343E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>40</v>
       </c>
@@ -889,19 +808,15 @@
       <c r="D21" s="1">
         <v>0.2</v>
       </c>
-      <c r="E21" s="1">
-        <v>3.7</v>
+      <c r="E21">
+        <v>15.617700000000001</v>
       </c>
       <c r="F21">
         <f t="shared" si="0"/>
-        <v>15.617700000000001</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="1"/>
         <v>6.402991477618343E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>55</v>
       </c>
@@ -914,19 +829,15 @@
       <c r="D22" s="1">
         <v>0.1</v>
       </c>
-      <c r="E22" s="1">
-        <v>3.7</v>
+      <c r="E22">
+        <v>15.617700000000001</v>
       </c>
       <c r="F22">
         <f t="shared" si="0"/>
-        <v>15.617700000000001</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="1"/>
         <v>6.402991477618343E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>44</v>
       </c>
@@ -939,19 +850,15 @@
       <c r="D23" s="1">
         <v>-0.1</v>
       </c>
-      <c r="E23" s="1">
-        <v>3.9</v>
+      <c r="E23">
+        <v>16.4619</v>
       </c>
       <c r="F23">
         <f t="shared" si="0"/>
-        <v>16.4619</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="1"/>
         <v>6.0746329403045821E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>50</v>
       </c>
@@ -964,19 +871,15 @@
       <c r="D24" s="1">
         <v>-0.2</v>
       </c>
-      <c r="E24" s="1">
-        <v>3.9</v>
+      <c r="E24">
+        <v>16.4619</v>
       </c>
       <c r="F24">
         <f t="shared" si="0"/>
-        <v>16.4619</v>
-      </c>
-      <c r="G24">
-        <f t="shared" si="1"/>
         <v>6.0746329403045821E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>53</v>
       </c>
@@ -990,18 +893,14 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>3.9</v>
+        <v>16.4619</v>
       </c>
       <c r="F25">
         <f t="shared" si="0"/>
-        <v>16.4619</v>
-      </c>
-      <c r="G25">
-        <f t="shared" si="1"/>
         <v>6.0746329403045821E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>62</v>
       </c>
@@ -1015,18 +914,14 @@
         <v>0.2</v>
       </c>
       <c r="E26">
-        <v>4.0999999999999996</v>
+        <v>17.306099999999997</v>
       </c>
       <c r="F26">
         <f t="shared" si="0"/>
-        <v>17.306099999999997</v>
-      </c>
-      <c r="G26">
-        <f t="shared" si="1"/>
         <v>5.7783093822409447E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>50</v>
       </c>
@@ -1039,19 +934,15 @@
       <c r="D27" s="1">
         <v>-0.1</v>
       </c>
-      <c r="E27" s="1">
-        <v>4.0999999999999996</v>
+      <c r="E27">
+        <v>17.306099999999997</v>
       </c>
       <c r="F27">
         <f t="shared" si="0"/>
-        <v>17.306099999999997</v>
-      </c>
-      <c r="G27">
-        <f t="shared" si="1"/>
         <v>5.7783093822409447E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>37</v>
       </c>
@@ -1065,18 +956,14 @@
         <v>-0.1</v>
       </c>
       <c r="E28">
-        <v>4.2</v>
+        <v>17.728200000000001</v>
       </c>
       <c r="F28">
         <f t="shared" si="0"/>
-        <v>17.728200000000001</v>
-      </c>
-      <c r="G28">
-        <f t="shared" si="1"/>
         <v>5.6407305874256831E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>68</v>
       </c>
@@ -1090,18 +977,14 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>4.2</v>
+        <v>17.728200000000001</v>
       </c>
       <c r="F29">
         <f t="shared" si="0"/>
-        <v>17.728200000000001</v>
-      </c>
-      <c r="G29">
-        <f t="shared" si="1"/>
         <v>5.6407305874256831E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>62</v>
       </c>
@@ -1115,18 +998,14 @@
         <v>0.2</v>
       </c>
       <c r="E30">
-        <v>4.2</v>
+        <v>17.728200000000001</v>
       </c>
       <c r="F30">
         <f t="shared" si="0"/>
-        <v>17.728200000000001</v>
-      </c>
-      <c r="G30">
-        <f t="shared" si="1"/>
         <v>5.6407305874256831E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>60</v>
       </c>
@@ -1140,18 +1019,14 @@
         <v>-0.1</v>
       </c>
       <c r="E31">
-        <v>4.3</v>
+        <v>18.150299999999998</v>
       </c>
       <c r="F31">
         <f t="shared" si="0"/>
-        <v>18.150299999999998</v>
-      </c>
-      <c r="G31">
-        <f t="shared" si="1"/>
         <v>5.5095508063227612E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>55</v>
       </c>
@@ -1165,18 +1040,14 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>4.3</v>
+        <v>18.150299999999998</v>
       </c>
       <c r="F32">
         <f t="shared" si="0"/>
-        <v>18.150299999999998</v>
-      </c>
-      <c r="G32">
-        <f t="shared" si="1"/>
         <v>5.5095508063227612E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>48</v>
       </c>
@@ -1190,18 +1061,14 @@
         <v>0.2</v>
       </c>
       <c r="E33">
-        <v>4.5999999999999996</v>
+        <v>19.416599999999999</v>
       </c>
       <c r="F33">
         <f t="shared" si="0"/>
-        <v>19.416599999999999</v>
-      </c>
-      <c r="G33">
-        <f t="shared" si="1"/>
         <v>5.150232275475624E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>53</v>
       </c>
@@ -1215,18 +1082,14 @@
         <v>0.3</v>
       </c>
       <c r="E34">
-        <v>4.5999999999999996</v>
+        <v>19.416599999999999</v>
       </c>
       <c r="F34">
         <f t="shared" si="0"/>
-        <v>19.416599999999999</v>
-      </c>
-      <c r="G34">
-        <f t="shared" si="1"/>
         <v>5.150232275475624E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>59</v>
       </c>
@@ -1240,18 +1103,14 @@
         <v>0.2</v>
       </c>
       <c r="E35">
-        <v>4.5999999999999996</v>
+        <v>19.416599999999999</v>
       </c>
       <c r="F35">
         <f t="shared" si="0"/>
-        <v>19.416599999999999</v>
-      </c>
-      <c r="G35">
-        <f t="shared" si="1"/>
         <v>5.150232275475624E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>36</v>
       </c>
@@ -1265,18 +1124,14 @@
         <v>0.2</v>
       </c>
       <c r="E36">
-        <v>4.7</v>
+        <v>19.838700000000003</v>
       </c>
       <c r="F36">
         <f t="shared" si="0"/>
-        <v>19.838700000000003</v>
-      </c>
-      <c r="G36">
-        <f t="shared" si="1"/>
         <v>5.0406528653591208E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>64</v>
       </c>
@@ -1290,18 +1145,14 @@
         <v>-0.2</v>
       </c>
       <c r="E37">
-        <v>4.7</v>
+        <v>19.838700000000003</v>
       </c>
       <c r="F37">
         <f t="shared" si="0"/>
-        <v>19.838700000000003</v>
-      </c>
-      <c r="G37">
-        <f t="shared" si="1"/>
         <v>5.0406528653591208E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>58</v>
       </c>
@@ -1314,19 +1165,15 @@
       <c r="D38" s="1">
         <v>0.2</v>
       </c>
-      <c r="E38" s="1">
-        <v>5.0999999999999996</v>
+      <c r="E38">
+        <v>21.527099999999997</v>
       </c>
       <c r="F38">
         <f t="shared" si="0"/>
-        <v>21.527099999999997</v>
-      </c>
-      <c r="G38">
-        <f t="shared" si="1"/>
         <v>4.6453075425858574E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>61</v>
       </c>
@@ -1339,19 +1186,15 @@
       <c r="D39" s="1">
         <v>0</v>
       </c>
-      <c r="E39" s="1">
-        <v>5.2</v>
+      <c r="E39">
+        <v>21.949200000000001</v>
       </c>
       <c r="F39">
         <f t="shared" si="0"/>
-        <v>21.949200000000001</v>
-      </c>
-      <c r="G39">
-        <f t="shared" si="1"/>
         <v>4.5559747052284362E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1365,18 +1208,14 @@
         <v>0.2</v>
       </c>
       <c r="E40">
-        <v>5.2</v>
+        <v>21.949200000000001</v>
       </c>
       <c r="F40">
         <f t="shared" si="0"/>
-        <v>21.949200000000001</v>
-      </c>
-      <c r="G40">
-        <f t="shared" si="1"/>
         <v>4.5559747052284362E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>59</v>
       </c>
@@ -1389,19 +1228,15 @@
       <c r="D41" s="1">
         <v>0.1</v>
       </c>
-      <c r="E41" s="1">
-        <v>5.5</v>
+      <c r="E41">
+        <v>23.215499999999999</v>
       </c>
       <c r="F41">
         <f t="shared" si="0"/>
-        <v>23.215499999999999</v>
-      </c>
-      <c r="G41">
-        <f t="shared" si="1"/>
         <v>4.3074669940341585E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>50</v>
       </c>
@@ -1415,18 +1250,14 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>5.5</v>
+        <v>23.215499999999999</v>
       </c>
       <c r="F42">
         <f t="shared" si="0"/>
-        <v>23.215499999999999</v>
-      </c>
-      <c r="G42">
-        <f t="shared" si="1"/>
         <v>4.3074669940341585E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>53</v>
       </c>
@@ -1440,18 +1271,14 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <v>5.8</v>
+        <v>24.4818</v>
       </c>
       <c r="F43">
         <f t="shared" si="0"/>
-        <v>24.4818</v>
-      </c>
-      <c r="G43">
-        <f t="shared" si="1"/>
         <v>4.0846669771013568E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>64</v>
       </c>
@@ -1464,19 +1291,15 @@
       <c r="D44" s="1">
         <v>0</v>
       </c>
-      <c r="E44" s="1">
-        <v>5.9</v>
+      <c r="E44">
+        <v>24.903900000000004</v>
       </c>
       <c r="F44">
         <f t="shared" si="0"/>
-        <v>24.903900000000004</v>
-      </c>
-      <c r="G44">
-        <f t="shared" si="1"/>
         <v>4.0154353334216721E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>46</v>
       </c>
@@ -1489,19 +1312,15 @@
       <c r="D45" s="1">
         <v>0</v>
       </c>
-      <c r="E45" s="1">
-        <v>6.2</v>
+      <c r="E45">
+        <v>26.170200000000001</v>
       </c>
       <c r="F45">
         <f t="shared" si="0"/>
-        <v>26.170200000000001</v>
-      </c>
-      <c r="G45">
-        <f t="shared" si="1"/>
         <v>3.8211400753528822E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>53</v>
       </c>
@@ -1515,18 +1334,14 @@
         <v>0.2</v>
       </c>
       <c r="E46">
-        <v>6.2</v>
+        <v>26.170200000000001</v>
       </c>
       <c r="F46">
         <f t="shared" si="0"/>
-        <v>26.170200000000001</v>
-      </c>
-      <c r="G46">
-        <f t="shared" si="1"/>
         <v>3.8211400753528822E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>48</v>
       </c>
@@ -1539,19 +1354,15 @@
       <c r="D47" s="1">
         <v>0</v>
       </c>
-      <c r="E47" s="1">
-        <v>6.9</v>
+      <c r="E47">
+        <v>29.124900000000004</v>
       </c>
       <c r="F47">
         <f t="shared" si="0"/>
-        <v>29.124900000000004</v>
-      </c>
-      <c r="G47">
-        <f t="shared" si="1"/>
         <v>3.4334881836504155E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>52</v>
       </c>
@@ -1565,18 +1376,14 @@
         <v>0.2</v>
       </c>
       <c r="E48">
-        <v>7.2</v>
+        <v>30.391200000000001</v>
       </c>
       <c r="F48">
         <f t="shared" si="0"/>
-        <v>30.391200000000001</v>
-      </c>
-      <c r="G48">
-        <f t="shared" si="1"/>
         <v>3.290426175998315E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>49</v>
       </c>
@@ -1589,19 +1396,15 @@
       <c r="D49" s="1">
         <v>0</v>
       </c>
-      <c r="E49" s="1">
-        <v>7.3</v>
+      <c r="E49">
+        <v>30.813299999999998</v>
       </c>
       <c r="F49">
         <f t="shared" si="0"/>
-        <v>30.813299999999998</v>
-      </c>
-      <c r="G49">
-        <f t="shared" si="1"/>
         <v>3.2453518448202566E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>46</v>
       </c>
@@ -1614,19 +1417,15 @@
       <c r="D50" s="1">
         <v>0.1</v>
       </c>
-      <c r="E50" s="1">
-        <v>7.7</v>
+      <c r="E50">
+        <v>32.5017</v>
       </c>
       <c r="F50">
         <f t="shared" si="0"/>
-        <v>32.5017</v>
-      </c>
-      <c r="G50">
-        <f t="shared" si="1"/>
         <v>3.0767621385958274E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>45</v>
       </c>
@@ -1640,18 +1439,14 @@
         <v>0.2</v>
       </c>
       <c r="E51">
-        <v>7.7</v>
+        <v>32.5017</v>
       </c>
       <c r="F51">
         <f t="shared" si="0"/>
-        <v>32.5017</v>
-      </c>
-      <c r="G51">
-        <f t="shared" si="1"/>
         <v>3.0767621385958274E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>40</v>
       </c>
@@ -1664,19 +1459,15 @@
       <c r="D52" s="1">
         <v>0.2</v>
       </c>
-      <c r="E52" s="1">
-        <v>8.4</v>
+      <c r="E52">
+        <v>35.456400000000002</v>
       </c>
       <c r="F52">
         <f t="shared" si="0"/>
-        <v>35.456400000000002</v>
-      </c>
-      <c r="G52">
-        <f t="shared" si="1"/>
         <v>2.8203652937128416E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>57</v>
       </c>
@@ -1689,19 +1480,15 @@
       <c r="D53" s="1">
         <v>0.1</v>
       </c>
-      <c r="E53" s="1">
-        <v>8.6</v>
+      <c r="E53">
+        <v>36.300599999999996</v>
       </c>
       <c r="F53">
         <f t="shared" si="0"/>
-        <v>36.300599999999996</v>
-      </c>
-      <c r="G53">
-        <f t="shared" si="1"/>
         <v>2.7547754031613806E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>46</v>
       </c>
@@ -1714,19 +1501,15 @@
       <c r="D54" s="1">
         <v>0</v>
       </c>
-      <c r="E54" s="1">
-        <v>8.6999999999999993</v>
+      <c r="E54">
+        <v>36.722699999999996</v>
       </c>
       <c r="F54">
         <f t="shared" si="0"/>
-        <v>36.722699999999996</v>
-      </c>
-      <c r="G54">
-        <f t="shared" si="1"/>
         <v>2.7231113180675715E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -1739,19 +1522,15 @@
       <c r="D55" s="1">
         <v>0.1</v>
       </c>
-      <c r="E55" s="1">
-        <v>9.1</v>
+      <c r="E55">
+        <v>38.411099999999998</v>
       </c>
       <c r="F55">
         <f t="shared" si="0"/>
-        <v>38.411099999999998</v>
-      </c>
-      <c r="G55">
-        <f t="shared" si="1"/>
         <v>2.6034141172733925E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>40</v>
       </c>
@@ -1765,18 +1544,14 @@
         <v>0.1</v>
       </c>
       <c r="E56">
-        <v>9.3000000000000007</v>
+        <v>39.255300000000005</v>
       </c>
       <c r="F56">
         <f t="shared" si="0"/>
-        <v>39.255300000000005</v>
-      </c>
-      <c r="G56">
-        <f t="shared" si="1"/>
         <v>2.547426716901921E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>66</v>
       </c>
@@ -1789,19 +1564,15 @@
       <c r="D57" s="1">
         <v>0</v>
       </c>
-      <c r="E57" s="1">
-        <v>9.4</v>
+      <c r="E57">
+        <v>39.677400000000006</v>
       </c>
       <c r="F57">
         <f t="shared" si="0"/>
-        <v>39.677400000000006</v>
-      </c>
-      <c r="G57">
-        <f t="shared" si="1"/>
         <v>2.5203264326795604E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>40</v>
       </c>
@@ -1815,18 +1586,14 @@
         <v>0.1</v>
       </c>
       <c r="E58">
-        <v>9.5</v>
+        <v>40.099499999999999</v>
       </c>
       <c r="F58">
         <f t="shared" si="0"/>
-        <v>40.099499999999999</v>
-      </c>
-      <c r="G58">
-        <f t="shared" si="1"/>
         <v>2.493796680756618E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>39</v>
       </c>
@@ -1840,18 +1607,14 @@
         <v>0</v>
       </c>
       <c r="E59">
-        <v>10.3</v>
+        <v>43.476300000000002</v>
       </c>
       <c r="F59">
         <f t="shared" si="0"/>
-        <v>43.476300000000002</v>
-      </c>
-      <c r="G59">
-        <f t="shared" si="1"/>
         <v>2.3001037346784339E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>50</v>
       </c>
@@ -1865,18 +1628,14 @@
         <v>0.1</v>
       </c>
       <c r="E60">
-        <v>11.7</v>
+        <v>49.3857</v>
       </c>
       <c r="F60">
         <f t="shared" si="0"/>
-        <v>49.3857</v>
-      </c>
-      <c r="G60">
-        <f t="shared" si="1"/>
         <v>2.0248776467681941E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>61</v>
       </c>
@@ -1889,19 +1648,15 @@
       <c r="D61" s="1">
         <v>-0.2</v>
       </c>
-      <c r="E61" s="1">
-        <v>11.9</v>
+      <c r="E61">
+        <v>50.229900000000001</v>
       </c>
       <c r="F61">
         <f t="shared" si="0"/>
-        <v>50.229900000000001</v>
-      </c>
-      <c r="G61">
-        <f t="shared" si="1"/>
         <v>1.9908460896796529E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>40</v>
       </c>
@@ -1914,19 +1669,15 @@
       <c r="D62" s="1">
         <v>0.1</v>
       </c>
-      <c r="E62" s="1">
-        <v>12.1</v>
+      <c r="E62">
+        <v>51.074100000000001</v>
       </c>
       <c r="F62">
         <f t="shared" si="0"/>
-        <v>51.074100000000001</v>
-      </c>
-      <c r="G62">
-        <f t="shared" si="1"/>
         <v>1.9579395427427992E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>48</v>
       </c>
@@ -1940,18 +1691,14 @@
         <v>0.2</v>
       </c>
       <c r="E63">
-        <v>12.1</v>
+        <v>51.074100000000001</v>
       </c>
       <c r="F63">
         <f t="shared" si="0"/>
-        <v>51.074100000000001</v>
-      </c>
-      <c r="G63">
-        <f t="shared" si="1"/>
         <v>1.9579395427427992E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>64</v>
       </c>
@@ -1964,19 +1711,15 @@
       <c r="D64" s="1">
         <v>0</v>
       </c>
-      <c r="E64" s="1">
-        <v>13.9</v>
+      <c r="E64">
+        <v>58.671900000000001</v>
       </c>
       <c r="F64">
         <f t="shared" si="0"/>
-        <v>58.671900000000001</v>
-      </c>
-      <c r="G64">
-        <f t="shared" si="1"/>
         <v>1.7043934149056021E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>70</v>
       </c>
@@ -1990,18 +1733,14 @@
         <v>0.1</v>
       </c>
       <c r="E65">
-        <v>13.9</v>
+        <v>58.671900000000001</v>
       </c>
       <c r="F65">
         <f t="shared" si="0"/>
-        <v>58.671900000000001</v>
-      </c>
-      <c r="G65">
-        <f t="shared" si="1"/>
         <v>1.7043934149056021E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>34</v>
       </c>
@@ -2015,18 +1754,14 @@
         <v>0.1</v>
       </c>
       <c r="E66">
-        <v>15.1</v>
+        <v>63.737099999999998</v>
       </c>
       <c r="F66">
         <f t="shared" si="0"/>
-        <v>63.737099999999998</v>
-      </c>
-      <c r="G66">
-        <f t="shared" si="1"/>
         <v>1.5689449316018459E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>54</v>
       </c>
@@ -2039,19 +1774,15 @@
       <c r="D67" s="1">
         <v>0.1</v>
       </c>
-      <c r="E67" s="1">
-        <v>15.5</v>
+      <c r="E67">
+        <v>65.4255</v>
       </c>
       <c r="F67">
-        <f t="shared" ref="F67:F105" si="2">E67*4.221</f>
-        <v>65.4255</v>
-      </c>
-      <c r="G67">
-        <f t="shared" ref="G67:G105" si="3">1/F67</f>
+        <f t="shared" ref="F67:F105" si="1">1/E67</f>
         <v>1.5284560301411529E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>70</v>
       </c>
@@ -2065,18 +1796,14 @@
         <v>0</v>
       </c>
       <c r="E68">
-        <v>15.7</v>
+        <v>66.2697</v>
       </c>
       <c r="F68">
-        <f t="shared" si="2"/>
-        <v>66.2697</v>
-      </c>
-      <c r="G68">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.5089852526871254E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>49</v>
       </c>
@@ -2090,18 +1817,14 @@
         <v>0.2</v>
       </c>
       <c r="E69">
-        <v>16</v>
+        <v>67.536000000000001</v>
       </c>
       <c r="F69">
-        <f t="shared" si="2"/>
-        <v>67.536000000000001</v>
-      </c>
-      <c r="G69">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.4806917791992419E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>62</v>
       </c>
@@ -2114,19 +1837,15 @@
       <c r="D70" s="1">
         <v>0.3</v>
       </c>
-      <c r="E70" s="1">
-        <v>16.899999999999999</v>
+      <c r="E70">
+        <v>71.33489999999999</v>
       </c>
       <c r="F70">
-        <f t="shared" si="2"/>
-        <v>71.33489999999999</v>
-      </c>
-      <c r="G70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.4018383708395192E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>36</v>
       </c>
@@ -2140,18 +1859,14 @@
         <v>0.1</v>
       </c>
       <c r="E71">
-        <v>17.7</v>
+        <v>74.711699999999993</v>
       </c>
       <c r="F71">
-        <f t="shared" si="2"/>
-        <v>74.711699999999993</v>
-      </c>
-      <c r="G71">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.3384784444738911E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>58</v>
       </c>
@@ -2165,18 +1880,14 @@
         <v>0.1</v>
       </c>
       <c r="E72">
-        <v>17.8</v>
+        <v>75.133800000000008</v>
       </c>
       <c r="F72">
-        <f t="shared" si="2"/>
-        <v>75.133800000000008</v>
-      </c>
-      <c r="G72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.3309589026510037E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>54</v>
       </c>
@@ -2190,18 +1901,14 @@
         <v>0</v>
       </c>
       <c r="E73">
-        <v>18.2</v>
+        <v>76.822199999999995</v>
       </c>
       <c r="F73">
-        <f t="shared" si="2"/>
-        <v>76.822199999999995</v>
-      </c>
-      <c r="G73">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.3017070586366962E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>64</v>
       </c>
@@ -2215,18 +1922,14 @@
         <v>0.1</v>
       </c>
       <c r="E74">
-        <v>20.2</v>
+        <v>85.264200000000002</v>
       </c>
       <c r="F74">
-        <f t="shared" si="2"/>
-        <v>85.264200000000002</v>
-      </c>
-      <c r="G74">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.1728251716429638E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>44</v>
       </c>
@@ -2240,18 +1943,14 @@
         <v>0.1</v>
       </c>
       <c r="E75">
-        <v>22.3</v>
+        <v>94.12830000000001</v>
       </c>
       <c r="F75">
-        <f t="shared" si="2"/>
-        <v>94.12830000000001</v>
-      </c>
-      <c r="G75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0623797518918326E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>53</v>
       </c>
@@ -2265,18 +1964,14 @@
         <v>0.1</v>
       </c>
       <c r="E76">
-        <v>22.8</v>
+        <v>96.238800000000012</v>
       </c>
       <c r="F76">
-        <f t="shared" si="2"/>
-        <v>96.238800000000012</v>
-      </c>
-      <c r="G76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.0390819503152574E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>54</v>
       </c>
@@ -2289,19 +1984,15 @@
       <c r="D77" s="1">
         <v>-0.1</v>
       </c>
-      <c r="E77" s="1">
-        <v>24.1</v>
+      <c r="E77">
+        <v>101.7261</v>
       </c>
       <c r="F77">
-        <f t="shared" si="2"/>
-        <v>101.7261</v>
-      </c>
-      <c r="G77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>9.8303188660530585E-3</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>44</v>
       </c>
@@ -2315,18 +2006,14 @@
         <v>0</v>
       </c>
       <c r="E78">
-        <v>24.3</v>
+        <v>102.5703</v>
       </c>
       <c r="F78">
-        <f t="shared" si="2"/>
-        <v>102.5703</v>
-      </c>
-      <c r="G78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>9.7494108918468603E-3</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>52</v>
       </c>
@@ -2340,18 +2027,14 @@
         <v>0</v>
       </c>
       <c r="E79">
-        <v>25.3</v>
+        <v>106.79130000000001</v>
       </c>
       <c r="F79">
-        <f t="shared" si="2"/>
-        <v>106.79130000000001</v>
-      </c>
-      <c r="G79">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>9.3640586826829516E-3</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>56</v>
       </c>
@@ -2364,19 +2047,15 @@
       <c r="D80" s="1">
         <v>0.1</v>
       </c>
-      <c r="E80" s="1">
-        <v>27.4</v>
+      <c r="E80">
+        <v>115.6554</v>
       </c>
       <c r="F80">
-        <f t="shared" si="2"/>
-        <v>115.6554</v>
-      </c>
-      <c r="G80">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>8.6463753529882736E-3</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>47</v>
       </c>
@@ -2390,18 +2069,14 @@
         <v>0</v>
       </c>
       <c r="E81">
-        <v>27.9</v>
+        <v>117.7659</v>
       </c>
       <c r="F81">
-        <f t="shared" si="2"/>
-        <v>117.7659</v>
-      </c>
-      <c r="G81">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>8.4914223896730718E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>53</v>
       </c>
@@ -2415,18 +2090,14 @@
         <v>0</v>
       </c>
       <c r="E82">
-        <v>28.3</v>
+        <v>119.4543</v>
       </c>
       <c r="F82">
-        <f t="shared" si="2"/>
-        <v>119.4543</v>
-      </c>
-      <c r="G82">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>8.3714022852253954E-3</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>48</v>
       </c>
@@ -2440,18 +2111,14 @@
         <v>0.1</v>
       </c>
       <c r="E83">
-        <v>43.3</v>
+        <v>182.76929999999999</v>
       </c>
       <c r="F83">
-        <f t="shared" si="2"/>
-        <v>182.76929999999999</v>
-      </c>
-      <c r="G83">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>5.4713783988886537E-3</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>51</v>
       </c>
@@ -2464,19 +2131,15 @@
       <c r="D84" s="1">
         <v>-0.1</v>
       </c>
-      <c r="E84" s="1">
-        <v>3000000</v>
+      <c r="E84">
+        <v>12663000</v>
       </c>
       <c r="F84">
-        <f t="shared" si="2"/>
-        <v>12663000</v>
-      </c>
-      <c r="G84">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>7.8970228223959566E-8</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>46</v>
       </c>
@@ -2489,19 +2152,15 @@
       <c r="D85" s="1">
         <v>-0.2</v>
       </c>
-      <c r="E85" s="1">
-        <v>3000000</v>
+      <c r="E85">
+        <v>12663000</v>
       </c>
       <c r="F85">
-        <f t="shared" si="2"/>
-        <v>12663000</v>
-      </c>
-      <c r="G85">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>7.8970228223959566E-8</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>45</v>
       </c>
@@ -2514,19 +2173,15 @@
       <c r="D86" s="1">
         <v>-0.2</v>
       </c>
-      <c r="E86" s="1">
-        <v>5000000</v>
+      <c r="E86">
+        <v>21105000</v>
       </c>
       <c r="F86">
-        <f t="shared" si="2"/>
-        <v>21105000</v>
-      </c>
-      <c r="G86">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4.738213693437574E-8</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>14</v>
       </c>
@@ -2539,19 +2194,15 @@
       <c r="D87" s="1">
         <v>0.2</v>
       </c>
-      <c r="E87" s="1">
-        <v>5000000</v>
+      <c r="E87">
+        <v>21105000</v>
       </c>
       <c r="F87">
-        <f t="shared" si="2"/>
-        <v>21105000</v>
-      </c>
-      <c r="G87">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4.738213693437574E-8</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>66</v>
       </c>
@@ -2564,19 +2215,15 @@
       <c r="D88" s="1">
         <v>0.1</v>
       </c>
-      <c r="E88" s="1">
-        <v>5000000</v>
+      <c r="E88">
+        <v>21105000</v>
       </c>
       <c r="F88">
-        <f t="shared" si="2"/>
-        <v>21105000</v>
-      </c>
-      <c r="G88">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4.738213693437574E-8</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>12</v>
       </c>
@@ -2589,19 +2236,15 @@
       <c r="D89" s="1">
         <v>0.1</v>
       </c>
-      <c r="E89" s="1">
-        <v>5000000</v>
+      <c r="E89">
+        <v>21105000</v>
       </c>
       <c r="F89">
-        <f t="shared" si="2"/>
-        <v>21105000</v>
-      </c>
-      <c r="G89">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4.738213693437574E-8</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>23</v>
       </c>
@@ -2614,19 +2257,15 @@
       <c r="D90" s="1">
         <v>-0.1</v>
       </c>
-      <c r="E90" s="1">
-        <v>5000000</v>
+      <c r="E90">
+        <v>21105000</v>
       </c>
       <c r="F90">
-        <f t="shared" si="2"/>
-        <v>21105000</v>
-      </c>
-      <c r="G90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4.738213693437574E-8</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>68</v>
       </c>
@@ -2640,18 +2279,14 @@
         <v>0</v>
       </c>
       <c r="E91">
-        <v>5000000</v>
+        <v>21105000</v>
       </c>
       <c r="F91">
-        <f t="shared" si="2"/>
-        <v>21105000</v>
-      </c>
-      <c r="G91">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4.738213693437574E-8</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>46</v>
       </c>
@@ -2664,19 +2299,15 @@
       <c r="D92" s="1">
         <v>0.2</v>
       </c>
-      <c r="E92" s="1">
-        <v>5000000</v>
+      <c r="E92">
+        <v>21105000</v>
       </c>
       <c r="F92">
-        <f t="shared" si="2"/>
-        <v>21105000</v>
-      </c>
-      <c r="G92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4.738213693437574E-8</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>24</v>
       </c>
@@ -2690,18 +2321,14 @@
         <v>-0.3</v>
       </c>
       <c r="E93">
-        <v>5000000</v>
+        <v>21105000</v>
       </c>
       <c r="F93">
-        <f t="shared" si="2"/>
-        <v>21105000</v>
-      </c>
-      <c r="G93">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4.738213693437574E-8</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>64</v>
       </c>
@@ -2715,18 +2342,14 @@
         <v>-0.2</v>
       </c>
       <c r="E94">
-        <v>5000000</v>
+        <v>21105000</v>
       </c>
       <c r="F94">
-        <f t="shared" si="2"/>
-        <v>21105000</v>
-      </c>
-      <c r="G94">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4.738213693437574E-8</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>65</v>
       </c>
@@ -2740,18 +2363,14 @@
         <v>0</v>
       </c>
       <c r="E95">
-        <v>5000000</v>
+        <v>21105000</v>
       </c>
       <c r="F95">
-        <f t="shared" si="2"/>
-        <v>21105000</v>
-      </c>
-      <c r="G95">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4.738213693437574E-8</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>13</v>
       </c>
@@ -2765,18 +2384,14 @@
         <v>0.2</v>
       </c>
       <c r="E96">
-        <v>5000000</v>
+        <v>21105000</v>
       </c>
       <c r="F96">
-        <f t="shared" si="2"/>
-        <v>21105000</v>
-      </c>
-      <c r="G96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4.738213693437574E-8</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>10</v>
       </c>
@@ -2790,18 +2405,14 @@
         <v>-0.2</v>
       </c>
       <c r="E97">
-        <v>5000000</v>
+        <v>21105000</v>
       </c>
       <c r="F97">
-        <f t="shared" si="2"/>
-        <v>21105000</v>
-      </c>
-      <c r="G97">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4.738213693437574E-8</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>69</v>
       </c>
@@ -2815,18 +2426,14 @@
         <v>0.2</v>
       </c>
       <c r="E98">
-        <v>5000000</v>
+        <v>21105000</v>
       </c>
       <c r="F98">
-        <f t="shared" si="2"/>
-        <v>21105000</v>
-      </c>
-      <c r="G98">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4.738213693437574E-8</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>56</v>
       </c>
@@ -2840,18 +2447,14 @@
         <v>-0.2</v>
       </c>
       <c r="E99">
-        <v>5000000</v>
+        <v>21105000</v>
       </c>
       <c r="F99">
-        <f t="shared" si="2"/>
-        <v>21105000</v>
-      </c>
-      <c r="G99">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4.738213693437574E-8</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>39</v>
       </c>
@@ -2864,19 +2467,15 @@
       <c r="D100" s="1">
         <v>-0.3</v>
       </c>
-      <c r="E100" s="1">
-        <v>5000000</v>
+      <c r="E100">
+        <v>21105000</v>
       </c>
       <c r="F100">
-        <f t="shared" si="2"/>
-        <v>21105000</v>
-      </c>
-      <c r="G100">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4.738213693437574E-8</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>49</v>
       </c>
@@ -2890,18 +2489,14 @@
         <v>0.3</v>
       </c>
       <c r="E101">
-        <v>5000000</v>
+        <v>21105000</v>
       </c>
       <c r="F101">
-        <f t="shared" si="2"/>
-        <v>21105000</v>
-      </c>
-      <c r="G101">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4.738213693437574E-8</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>65</v>
       </c>
@@ -2915,18 +2510,14 @@
         <v>0.2</v>
       </c>
       <c r="E102">
-        <v>5000000</v>
+        <v>21105000</v>
       </c>
       <c r="F102">
-        <f t="shared" si="2"/>
-        <v>21105000</v>
-      </c>
-      <c r="G102">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4.738213693437574E-8</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>56</v>
       </c>
@@ -2940,18 +2531,14 @@
         <v>0.3</v>
       </c>
       <c r="E103">
-        <v>5000000</v>
+        <v>21105000</v>
       </c>
       <c r="F103">
-        <f t="shared" si="2"/>
-        <v>21105000</v>
-      </c>
-      <c r="G103">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4.738213693437574E-8</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>63</v>
       </c>
@@ -2965,18 +2552,14 @@
         <v>-0.2</v>
       </c>
       <c r="E104">
-        <v>5000000</v>
+        <v>21105000</v>
       </c>
       <c r="F104">
-        <f t="shared" si="2"/>
-        <v>21105000</v>
-      </c>
-      <c r="G104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4.738213693437574E-8</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>40</v>
       </c>
@@ -2990,21 +2573,14 @@
         <v>-0.2</v>
       </c>
       <c r="E105">
-        <v>5000000</v>
+        <v>21105000</v>
       </c>
       <c r="F105">
-        <f t="shared" si="2"/>
-        <v>21105000</v>
-      </c>
-      <c r="G105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>4.738213693437574E-8</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E113">
-    <sortCondition ref="E1:E113"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>